--- a/teachers.xlsx
+++ b/teachers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TCS\Downloads\noname_sas1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\II-II\COMP 207 COMPUTER PROJECT II\Smart-Attendance-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FCC550-293C-4085-B61C-4B6E04E987D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B47F31-E115-41B5-AD8B-7560190C0844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1545" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -40,67 +40,67 @@
     <t>password</t>
   </si>
   <si>
-    <t>Mr. Bipesh Subedi</t>
-  </si>
-  <si>
-    <t>bipesh.subedi@ku.edu.np</t>
-  </si>
-  <si>
     <t>DoCSE</t>
   </si>
   <si>
-    <t>bipesh.subedi</t>
-  </si>
-  <si>
-    <t>ce2subedi1</t>
-  </si>
-  <si>
-    <t>Mr. Gobinda Subedi</t>
-  </si>
-  <si>
-    <t>gobinda.subedi@ku.edu.np</t>
-  </si>
-  <si>
-    <t>gobinda.subedi</t>
-  </si>
-  <si>
-    <t>ce2subedi2</t>
-  </si>
-  <si>
-    <t>Prof. Dr. Gajendra Sharma</t>
-  </si>
-  <si>
-    <t>gajendra.sharma@ku.edu.np</t>
-  </si>
-  <si>
-    <t>gajendra.sharma</t>
-  </si>
-  <si>
-    <t>ce2sharma3</t>
-  </si>
-  <si>
-    <t>Mohan Chandra Adhikari</t>
-  </si>
-  <si>
-    <t>mohan.adhikari@ku.edu.np</t>
-  </si>
-  <si>
-    <t>mohan.adhikari</t>
-  </si>
-  <si>
-    <t>ce2adhikari4</t>
-  </si>
-  <si>
-    <t>Dr. Sushil Ghimire</t>
-  </si>
-  <si>
-    <t>sushil.ghimire@ku.edu.np</t>
-  </si>
-  <si>
-    <t>sushil.ghimire</t>
-  </si>
-  <si>
-    <t>ce2ghimire5</t>
+    <t>Mr. Rajan Thapa</t>
+  </si>
+  <si>
+    <t>rajan.thapa@ku.edu.np</t>
+  </si>
+  <si>
+    <t>rajan.thapa</t>
+  </si>
+  <si>
+    <t>ce2thapa1</t>
+  </si>
+  <si>
+    <t>Mr. Suman Karki</t>
+  </si>
+  <si>
+    <t>suman.karki@ku.edu.np</t>
+  </si>
+  <si>
+    <t>suman.karki</t>
+  </si>
+  <si>
+    <t>ce2karki2</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Prakash Basnet</t>
+  </si>
+  <si>
+    <t>prakash.basnet@ku.edu.np</t>
+  </si>
+  <si>
+    <t>prakash.basnet</t>
+  </si>
+  <si>
+    <t>ce2basnet3</t>
+  </si>
+  <si>
+    <t>Mohan Bahadur Rai</t>
+  </si>
+  <si>
+    <t>mohan.rai@ku.edu.np</t>
+  </si>
+  <si>
+    <t>mohan.rai</t>
+  </si>
+  <si>
+    <t>ce2rai4</t>
+  </si>
+  <si>
+    <t>Dr. Kishor Poudel</t>
+  </si>
+  <si>
+    <t>kishor.poudel@ku.edu.np</t>
+  </si>
+  <si>
+    <t>kishor.poudel</t>
+  </si>
+  <si>
+    <t>ce2poudel5</t>
   </si>
 </sst>
 </file>
@@ -482,16 +482,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>9841000001</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -511,7 +511,7 @@
         <v>9841000002</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -531,7 +531,7 @@
         <v>9841000003</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -551,7 +551,7 @@
         <v>9841000004</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -571,7 +571,7 @@
         <v>9841000005</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>

--- a/teachers.xlsx
+++ b/teachers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\II-II\COMP 207 COMPUTER PROJECT II\Smart-Attendance-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B47F31-E115-41B5-AD8B-7560190C0844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC845472-FA90-46DC-B692-D476B4A3A5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2595" yWindow="2595" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,27 +55,9 @@
     <t>ce2thapa1</t>
   </si>
   <si>
-    <t>Mr. Suman Karki</t>
-  </si>
-  <si>
-    <t>suman.karki@ku.edu.np</t>
-  </si>
-  <si>
-    <t>suman.karki</t>
-  </si>
-  <si>
     <t>ce2karki2</t>
   </si>
   <si>
-    <t>Prof. Dr. Prakash Basnet</t>
-  </si>
-  <si>
-    <t>prakash.basnet@ku.edu.np</t>
-  </si>
-  <si>
-    <t>prakash.basnet</t>
-  </si>
-  <si>
     <t>ce2basnet3</t>
   </si>
   <si>
@@ -101,13 +83,31 @@
   </si>
   <si>
     <t>ce2poudel5</t>
+  </si>
+  <si>
+    <t>Mr. Josh Karki</t>
+  </si>
+  <si>
+    <t>josh.karki@ku.edu.np</t>
+  </si>
+  <si>
+    <t>josh.karki</t>
+  </si>
+  <si>
+    <t>krishna.basnet@ku.edu.np</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Krishna Basnet</t>
+  </si>
+  <si>
+    <t>krishna.basnet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +119,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -141,14 +149,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -502,10 +513,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C3">
         <v>9841000002</v>
@@ -514,18 +525,18 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C4">
         <v>9841000003</v>
@@ -534,18 +545,18 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>9841000004</v>
@@ -554,18 +565,18 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>9841000005</v>
@@ -574,13 +585,17 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{C0B7616C-FBEF-4E23-BC2C-D6C29A47636E}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{86188300-4B66-4427-9B66-B16EAA0BCACA}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>